--- a/eval-suite/cases/012_dwb_order_center_f/mapping.xlsx
+++ b/eval-suite/cases/012_dwb_order_center_f/mapping.xlsx
@@ -2,40 +2,387 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24980" windowHeight="11800" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实体级mapping" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性级mapping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="22">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2563EB"/>
+        <bgColor rgb="FF2563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -43,15 +390,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -404,7 +1065,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -414,905 +1074,1115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <cols>
+    <col width="14" customWidth="1" min="3" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>源表schema</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>源表物理表名</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>源表schema*</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>源表中文名</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>源表别名</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>目标表schema</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>源表物理表名*</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>源表别名*</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>目标表逻辑schema*</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>目标表中文名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>目标表物理表名</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>目标表物理名称*</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>取数规则</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>关联&amp;限定条件</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>数据库类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>sdord</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>订单明细事实表</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>dwd_order_f</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>订单明细事实表</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>dof</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>where t.order_status NOT IN ('CANCELLED', 'DELETED')</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>主事实表</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>sdord</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>订单商品明细事实表</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>dwd_order_detail_f</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>订单商品明细事实表</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>dod</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>left join on t.order_id=od.order_id AND od.del_flag='N'</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>取第一条商品信息作为主商品</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="31" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>sdpay</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>支付事实表</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>dwd_payment_f</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>支付事实表</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>dpf</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>left join on t.order_id=pay.order_id AND pay.pay_status='SUCCESS'</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>取最新一条支付记录</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>sdlog</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>物流事实表</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>dwd_logistics_f</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>物流事实表</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>dlf</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>left join on t.order_id=log.order_id AND log.del_flag='N'</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>取最新物流信息</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>sdmar</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>优惠券使用事实表</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>dwd_coupon_use_f</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>优惠券使用事实表</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>dcu</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>left join on t.order_id=cu.order_id AND cu.use_status='USED'</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>取使用的优惠券信息</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>用户维度表</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>dim_user_f</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>用户维度表</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>duf</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>left join on t.user_id=u.user_id</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>用户基本信息</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>用户等级维度表</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>dim_user_level_f</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>用户等级维度表</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>dul</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>left join on u.level_id=ul.level_id</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>【复杂关联】订单→用户维表→等级维表</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>商品维度表</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>dim_product_f</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>商品维度表</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>dpf7</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>left join on od.product_id=p.product_id</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>商品基本信息</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>商品分类维度表</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>dim_product_category_f</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>商品分类维度表</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>dpc</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>left join on p.category_id=pc.category_id  -- 一级类目
 left join on pc.parent_id=pc2.category_id  -- 二级类目
 left join on pc2.parent_id=pc3.category_id  -- 三级类目</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>【复杂关联】商品→一级类目→二级类目→三级类目</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>品牌维度表</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>dim_brand_f</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>品牌维度表</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>dbf</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>left join on p.brand_id=b.brand_id</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>【复杂关联】订单明细→商品维表→品牌维表</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>店铺维度表</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>dim_shop_f</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>店铺维度表</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>dsf</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>left join on t.shop_id=s.shop_id</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>店铺基本信息</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>地区维度表</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>dim_region_f</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>地区维度表</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>drf</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>left join on t.province_code=r1.region_code  -- 省份
 left join on t.city_code=r2.region_code  -- 城市
 left join on t.district_code=r3.region_code  -- 区县</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>【复杂关联】多地区维度关联取省市县名称</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>仓库维度表</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>dim_warehouse_f</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>仓库维度表</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>dwf</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>left join on log.warehouse_id=wh.warehouse_id</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>【复杂关联】物流→仓库维表</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>支付方式维度表</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>dim_payment_method_f</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>支付方式维度表</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>dpm</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>left join on pay.pay_method=pm.method_code</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>支付方式名称</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>物流公司维度表</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>dim_logistics_company_f</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>物流公司维度表</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>dlc</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>left join on log.logistics_company=lc.company_code</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>物流公司信息</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>优惠券维度表</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>dim_coupon_f</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>优惠券维度表</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>dcf</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>left join on cu.coupon_id=c.coupon_id</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>优惠券信息</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>营销活动维度表</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>dim_activity_f</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>营销活动维度表</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>daf</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>left join on t.activity_id=act.activity_id</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>营销活动信息</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>sdref</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>退款事实表</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>dwd_refund_f</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>退款事实表</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>drf17</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>slord</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>订单中心宽表</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>dwb_order_center_f</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>left join on t.order_id=rf.order_id AND rf.refund_status='SUCCESS'</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>退款信息汇总</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1325,82 +2195,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O151"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>源Schema</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>源表物理表名</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>源表物理表别名</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>源表字段中文名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>源表字段名</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>源表字段类型</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>映射规则*</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>映射表达式</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>目标字段名*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>目标字段中文名</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>目标字段类型</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>数据标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="31" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -1446,7 +2330,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1469,8 +2353,9 @@
           <t>主键</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
@@ -1516,7 +2401,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,8 +2420,9 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -1582,7 +2468,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1601,8 +2487,9 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -1667,8 +2554,9 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -1714,7 +2602,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1733,8 +2621,9 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -1780,7 +2669,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1799,8 +2688,9 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -1846,7 +2736,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1865,8 +2755,9 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -1912,7 +2803,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1931,8 +2822,9 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
@@ -1956,21 +2848,9 @@
           <t>dlf</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -1997,8 +2877,9 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="137" customHeight="1">
       <c r="A11" t="n">
         <v>10</v>
       </c>
@@ -2044,7 +2925,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2063,8 +2944,9 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="152" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
@@ -2110,7 +2992,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2129,8 +3011,9 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="76" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
@@ -2176,7 +3059,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2195,6 +3078,7 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2242,7 +3126,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2261,6 +3145,7 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2308,7 +3193,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2327,6 +3212,7 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2374,7 +3260,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2393,6 +3279,7 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2440,7 +3327,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2459,6 +3346,7 @@
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2525,6 +3413,7 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +3480,7 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2638,7 +3528,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2657,6 +3547,7 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2723,6 +3614,7 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2770,7 +3662,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2789,6 +3681,7 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,7 +3729,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2855,6 +3748,7 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2921,6 +3815,7 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2987,6 +3882,7 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3053,6 +3949,7 @@
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3100,7 +3997,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3119,6 +4016,7 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3144,21 +4042,9 @@
           <t>duf</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3185,6 +4071,7 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3232,7 +4119,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3251,6 +4138,7 @@
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3298,7 +4186,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3317,6 +4205,7 @@
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3364,7 +4253,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3383,6 +4272,7 @@
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3430,7 +4320,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3449,6 +4339,7 @@
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3496,7 +4387,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3515,6 +4406,7 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3540,21 +4432,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3581,6 +4461,7 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3606,21 +4487,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3647,6 +4516,7 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3672,21 +4542,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3713,6 +4571,7 @@
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3738,21 +4597,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3779,6 +4626,7 @@
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3804,21 +4652,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3845,6 +4681,7 @@
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3870,21 +4707,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3911,6 +4736,7 @@
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3936,21 +4762,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3977,6 +4791,7 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4024,7 +4839,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4043,6 +4858,7 @@
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4109,6 +4925,7 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4156,7 +4973,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4175,6 +4992,7 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4222,7 +5040,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4241,6 +5059,7 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4266,21 +5085,9 @@
           <t>duf</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4307,6 +5114,7 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4332,21 +5140,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4373,6 +5169,7 @@
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4420,7 +5217,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4439,6 +5236,7 @@
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4486,7 +5284,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4505,6 +5303,7 @@
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4552,7 +5351,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4571,6 +5370,7 @@
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4618,7 +5418,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4637,6 +5437,7 @@
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4684,7 +5485,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4703,6 +5504,7 @@
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4750,7 +5552,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4769,6 +5571,7 @@
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4794,21 +5597,9 @@
           <t>dpc</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4835,6 +5626,7 @@
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4860,21 +5652,9 @@
           <t>dpc</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4901,6 +5681,7 @@
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4926,21 +5707,9 @@
           <t>dpc</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4967,6 +5736,7 @@
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4992,21 +5762,9 @@
           <t>dpc</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5033,6 +5791,7 @@
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5080,7 +5839,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5099,6 +5858,7 @@
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5146,7 +5906,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5165,6 +5925,7 @@
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5212,7 +5973,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5231,6 +5992,7 @@
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5278,7 +6040,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5297,6 +6059,7 @@
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5344,7 +6107,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5363,6 +6126,7 @@
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5410,7 +6174,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5429,6 +6193,7 @@
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5476,7 +6241,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5495,6 +6260,7 @@
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5542,7 +6308,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5561,6 +6327,7 @@
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5608,7 +6375,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5627,6 +6394,7 @@
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5674,7 +6442,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5693,6 +6461,7 @@
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5740,7 +6509,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5759,6 +6528,7 @@
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5825,6 +6595,7 @@
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5850,21 +6621,9 @@
           <t>dod</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5891,6 +6650,7 @@
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5916,21 +6676,9 @@
           <t>dod</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5957,6 +6705,7 @@
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5982,21 +6731,9 @@
           <t>dod</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -6023,6 +6760,7 @@
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6070,7 +6808,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6089,6 +6827,7 @@
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6136,7 +6875,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6155,6 +6894,7 @@
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6221,6 +6961,7 @@
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6287,6 +7028,7 @@
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6334,7 +7076,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6353,6 +7095,7 @@
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6400,7 +7143,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6419,6 +7162,7 @@
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6466,7 +7210,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6485,6 +7229,7 @@
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6510,21 +7255,9 @@
           <t>drf</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -6551,6 +7284,7 @@
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6598,7 +7332,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6617,6 +7351,7 @@
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6642,21 +7377,9 @@
           <t>drf</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -6683,6 +7406,7 @@
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6730,7 +7454,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6749,6 +7473,7 @@
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6774,21 +7499,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -6815,6 +7528,7 @@
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6862,7 +7576,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6881,6 +7595,7 @@
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6947,6 +7662,7 @@
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6994,7 +7710,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7013,6 +7729,7 @@
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7060,7 +7777,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7079,6 +7796,7 @@
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7126,7 +7844,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7145,6 +7863,7 @@
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7170,21 +7889,9 @@
           <t>drf</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -7211,6 +7918,7 @@
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7258,7 +7966,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7277,6 +7985,7 @@
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7302,21 +8011,9 @@
           <t>drf</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -7343,6 +8040,7 @@
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7390,7 +8088,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -7409,6 +8107,7 @@
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7456,7 +8155,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -7475,6 +8174,7 @@
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7500,21 +8200,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -7541,6 +8229,7 @@
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7588,7 +8277,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7607,6 +8296,7 @@
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7673,6 +8363,7 @@
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7720,7 +8411,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7739,6 +8430,7 @@
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7786,7 +8478,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7805,6 +8497,7 @@
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7852,7 +8545,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7871,6 +8564,7 @@
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7918,7 +8612,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7937,6 +8631,7 @@
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7984,7 +8679,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8003,6 +8698,7 @@
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8050,7 +8746,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -8069,6 +8765,7 @@
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8094,21 +8791,9 @@
           <t>dpm</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -8135,6 +8820,7 @@
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8201,6 +8887,7 @@
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8267,6 +8954,7 @@
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8314,7 +9002,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -8333,6 +9021,7 @@
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8380,7 +9069,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -8399,6 +9088,7 @@
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8446,7 +9136,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -8465,6 +9155,7 @@
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8490,21 +9181,9 @@
           <t>dpf</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -8531,6 +9210,7 @@
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8556,21 +9236,9 @@
           <t>dpf</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -8597,6 +9265,7 @@
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8644,7 +9313,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -8663,6 +9332,7 @@
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8710,7 +9380,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -8729,6 +9399,7 @@
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8776,7 +9447,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8795,6 +9466,7 @@
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8842,7 +9514,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8861,6 +9533,7 @@
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8886,21 +9559,9 @@
           <t>dlc</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -8927,6 +9588,7 @@
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8974,7 +9636,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8993,6 +9655,7 @@
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9040,7 +9703,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -9059,6 +9722,7 @@
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9084,21 +9748,9 @@
           <t>dwf</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -9125,6 +9777,7 @@
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9191,6 +9844,7 @@
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9238,7 +9892,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -9257,6 +9911,7 @@
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9304,7 +9959,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -9323,6 +9978,7 @@
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9348,21 +10004,9 @@
           <t>dlf</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -9389,6 +10033,7 @@
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9436,7 +10081,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -9455,6 +10100,7 @@
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9502,7 +10148,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -9521,6 +10167,7 @@
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9587,6 +10234,7 @@
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9634,7 +10282,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -9653,6 +10301,7 @@
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9700,7 +10349,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -9719,6 +10368,7 @@
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9766,7 +10416,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9785,6 +10435,7 @@
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9851,6 +10502,7 @@
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9898,7 +10550,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -9917,6 +10569,7 @@
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9964,7 +10617,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -9983,6 +10636,7 @@
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10030,7 +10684,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -10049,6 +10703,7 @@
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10096,7 +10751,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -10115,6 +10770,7 @@
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10140,21 +10796,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10181,6 +10825,7 @@
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10206,21 +10851,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10247,6 +10880,7 @@
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10272,21 +10906,9 @@
           <t>dcu</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10313,6 +10935,7 @@
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10338,21 +10961,9 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10379,6 +10990,7 @@
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10426,7 +11038,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -10445,6 +11057,7 @@
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10492,7 +11105,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -10511,6 +11124,7 @@
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10577,6 +11191,7 @@
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10624,7 +11239,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -10643,6 +11258,7 @@
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10690,7 +11306,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -10709,6 +11325,7 @@
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10775,6 +11392,7 @@
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10822,7 +11440,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10841,6 +11459,7 @@
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -10888,7 +11507,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10907,6 +11526,7 @@
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10932,21 +11552,9 @@
           <t>drf17</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10973,6 +11581,7 @@
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10998,21 +11607,9 @@
           <t>drf17</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -11039,6 +11636,7 @@
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11085,6 +11683,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11131,6 +11730,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11177,6 +11777,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11223,6 +11824,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eval-suite/cases/012_dwb_order_center_f/mapping.xlsx
+++ b/eval-suite/cases/012_dwb_order_center_f/mapping.xlsx
@@ -1195,10 +1195,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>where t.order_status NOT IN ('CANCELLED', 'DELETED')</t>
@@ -1209,7 +1208,6 @@
           <t>主事实表</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1252,10 +1250,9 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>left join on t.order_id=od.order_id AND od.del_flag='N'</t>
@@ -1266,7 +1263,6 @@
           <t>取第一条商品信息作为主商品</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4" ht="31" customHeight="1">
       <c r="A4" t="n">
@@ -1309,10 +1305,9 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>left join on t.order_id=pay.order_id AND pay.pay_status='SUCCESS'</t>
@@ -1323,7 +1318,6 @@
           <t>取最新一条支付记录</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1366,10 +1360,9 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>left join on t.order_id=log.order_id AND log.del_flag='N'</t>
@@ -1380,7 +1373,6 @@
           <t>取最新物流信息</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1423,10 +1415,9 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>left join on t.order_id=cu.order_id AND cu.use_status='USED'</t>
@@ -1437,7 +1428,6 @@
           <t>取使用的优惠券信息</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1480,10 +1470,9 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>left join on t.user_id=u.user_id</t>
@@ -1494,7 +1483,6 @@
           <t>用户基本信息</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1537,10 +1525,9 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>left join on u.level_id=ul.level_id</t>
@@ -1551,7 +1538,6 @@
           <t>【复杂关联】订单→用户维表→等级维表</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,10 +1580,9 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>left join on od.product_id=p.product_id</t>
@@ -1608,7 +1593,6 @@
           <t>商品基本信息</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,10 +1635,9 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>left join on p.category_id=pc.category_id  -- 一级类目
@@ -1667,7 +1650,6 @@
           <t>【复杂关联】商品→一级类目→二级类目→三级类目</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,10 +1692,9 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>left join on p.brand_id=b.brand_id</t>
@@ -1724,7 +1705,6 @@
           <t>【复杂关联】订单明细→商品维表→品牌维表</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,10 +1747,9 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>left join on t.shop_id=s.shop_id</t>
@@ -1781,7 +1760,6 @@
           <t>店铺基本信息</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1824,10 +1802,9 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>left join on t.province_code=r1.region_code  -- 省份
@@ -1840,7 +1817,6 @@
           <t>【复杂关联】多地区维度关联取省市县名称</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1883,10 +1859,9 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>left join on log.warehouse_id=wh.warehouse_id</t>
@@ -1897,7 +1872,6 @@
           <t>【复杂关联】物流→仓库维表</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1940,10 +1914,9 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>left join on pay.pay_method=pm.method_code</t>
@@ -1954,7 +1927,6 @@
           <t>支付方式名称</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1997,10 +1969,9 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>left join on log.logistics_company=lc.company_code</t>
@@ -2011,7 +1982,6 @@
           <t>物流公司信息</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2054,10 +2024,9 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>left join on cu.coupon_id=c.coupon_id</t>
@@ -2068,7 +2037,6 @@
           <t>优惠券信息</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2111,10 +2079,9 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>left join on t.activity_id=act.activity_id</t>
@@ -2125,7 +2092,6 @@
           <t>营销活动信息</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2168,10 +2134,9 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>dwb_order_center_f</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>dwb_order_center_i</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>left join on t.order_id=rf.order_id AND rf.refund_status='SUCCESS'</t>
@@ -2182,7 +2147,6 @@
           <t>退款信息汇总</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2353,7 +2317,6 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
@@ -2419,8 +2382,6 @@
           <t>varchar(64)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
@@ -2486,8 +2447,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
@@ -2553,8 +2512,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
@@ -2620,8 +2577,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
@@ -2687,8 +2642,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
@@ -2754,8 +2707,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
@@ -2821,8 +2772,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" t="n">
@@ -2848,9 +2797,6 @@
           <t>dlf</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -2876,8 +2822,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11" ht="137" customHeight="1">
       <c r="A11" t="n">
@@ -2943,8 +2887,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12" ht="152" customHeight="1">
       <c r="A12" t="n">
@@ -3010,8 +2952,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13" ht="76" customHeight="1">
       <c r="A13" t="n">
@@ -3077,8 +3017,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3144,8 +3082,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3211,8 +3147,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3278,8 +3212,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3345,8 +3277,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3412,8 +3342,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3479,8 +3407,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3546,8 +3472,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3613,8 +3537,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3680,8 +3602,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3747,8 +3667,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3814,8 +3732,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3881,8 +3797,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3948,8 +3862,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4015,8 +3927,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4042,9 +3952,6 @@
           <t>duf</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4070,8 +3977,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4137,8 +4042,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4204,8 +4107,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4271,8 +4172,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4338,8 +4237,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4405,8 +4302,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4432,9 +4327,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4460,8 +4352,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4487,9 +4377,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4515,8 +4402,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4542,9 +4427,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4570,8 +4452,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4597,9 +4477,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4625,8 +4502,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4652,9 +4527,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4680,8 +4552,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4707,9 +4577,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4735,8 +4602,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4762,9 +4627,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4790,8 +4652,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4857,8 +4717,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4924,8 +4782,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4991,8 +4847,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5058,8 +4912,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5085,9 +4937,6 @@
           <t>duf</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5113,8 +4962,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5140,9 +4987,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5168,8 +5012,6 @@
           <t>varchar(1)</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5235,8 +5077,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5302,8 +5142,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5369,8 +5207,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5436,8 +5272,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5503,8 +5337,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5570,8 +5402,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5597,9 +5427,6 @@
           <t>dpc</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5625,8 +5452,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5652,9 +5477,6 @@
           <t>dpc</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5680,8 +5502,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5707,9 +5527,6 @@
           <t>dpc</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5735,8 +5552,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5762,9 +5577,6 @@
           <t>dpc</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -5790,8 +5602,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5857,8 +5667,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5924,8 +5732,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5991,8 +5797,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6058,8 +5862,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6125,8 +5927,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6192,8 +5992,6 @@
           <t>decimal(10,2)</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6259,8 +6057,6 @@
           <t>decimal(10,4)</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6326,8 +6122,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6393,8 +6187,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6460,8 +6252,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6527,8 +6317,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6594,8 +6382,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6621,9 +6407,6 @@
           <t>dod</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -6649,8 +6432,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6676,9 +6457,6 @@
           <t>dod</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -6704,8 +6482,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6731,9 +6507,6 @@
           <t>dod</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -6759,8 +6532,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6826,8 +6597,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6893,8 +6662,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6960,8 +6727,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7027,8 +6792,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7094,8 +6857,6 @@
           <t>decimal(3,2)</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7161,8 +6922,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7228,8 +6987,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7255,9 +7012,6 @@
           <t>drf</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -7283,8 +7037,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7350,8 +7102,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7377,9 +7127,6 @@
           <t>drf</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -7405,8 +7152,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7472,8 +7217,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7499,9 +7242,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -7527,8 +7267,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7594,8 +7332,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7661,8 +7397,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7728,8 +7462,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7795,8 +7527,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7862,8 +7592,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7889,9 +7617,6 @@
           <t>drf</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -7917,8 +7642,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7984,8 +7707,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8011,9 +7732,6 @@
           <t>drf</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -8039,8 +7757,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8106,8 +7822,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8173,8 +7887,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8200,9 +7912,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -8228,8 +7937,6 @@
           <t>varchar(1000)</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8295,8 +8002,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8362,8 +8067,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8429,8 +8132,6 @@
           <t>decimal(10,6)</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8496,8 +8197,6 @@
           <t>decimal(10,6)</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8563,8 +8262,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8630,8 +8327,6 @@
           <t>varchar(64)</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8697,8 +8392,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8764,8 +8457,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8791,9 +8482,6 @@
           <t>dpm</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -8819,8 +8507,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8886,8 +8572,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8953,8 +8637,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9020,8 +8702,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9087,8 +8767,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9154,8 +8832,6 @@
           <t>decimal(10,2)</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -9181,9 +8857,6 @@
           <t>dpf</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -9209,8 +8882,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -9236,9 +8907,6 @@
           <t>dpf</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -9264,8 +8932,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9331,8 +8997,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -9398,8 +9062,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9465,8 +9127,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9532,8 +9192,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9559,9 +9217,6 @@
           <t>dlc</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -9587,8 +9242,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9654,8 +9307,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9721,8 +9372,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9748,9 +9397,6 @@
           <t>dwf</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -9776,8 +9422,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9843,8 +9487,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9910,8 +9552,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9977,8 +9617,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -10004,9 +9642,6 @@
           <t>dlf</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10032,8 +9667,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -10099,8 +9732,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -10166,8 +9797,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -10233,8 +9862,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -10300,8 +9927,6 @@
           <t>decimal(10,2)</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -10367,8 +9992,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10434,8 +10057,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10501,8 +10122,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10568,8 +10187,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10635,8 +10252,6 @@
           <t>decimal(10,2)</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10702,8 +10317,6 @@
           <t>decimal(10,2)</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10769,8 +10382,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10796,9 +10407,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10824,8 +10432,6 @@
           <t>varchar(1)</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10851,9 +10457,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10879,8 +10482,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10906,9 +10507,6 @@
           <t>dcu</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10934,8 +10532,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10961,9 +10557,6 @@
           <t>dof</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -10989,8 +10582,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -11056,8 +10647,6 @@
           <t>bigint</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11123,8 +10712,6 @@
           <t>varchar(64)</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11190,8 +10777,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11257,8 +10842,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11324,8 +10907,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11391,8 +10972,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11458,8 +11037,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -11525,8 +11102,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -11552,9 +11127,6 @@
           <t>drf17</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -11580,8 +11152,6 @@
           <t>varchar(1)</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11607,9 +11177,6 @@
           <t>drf17</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -11635,8 +11202,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11647,12 +11212,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -11683,7 +11242,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11694,12 +11252,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -11730,7 +11282,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11741,12 +11292,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -11777,7 +11322,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11788,12 +11332,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -11824,7 +11362,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eval-suite/cases/012_dwb_order_center_f/mapping.xlsx
+++ b/eval-suite/cases/012_dwb_order_center_f/mapping.xlsx
@@ -2194,7 +2194,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>源表物理表别名</t>
+          <t>源表别名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
